--- a/data/trans_orig/IP31KM04_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM04_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58753</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48616</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68558</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47287</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38527</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56321</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>37559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80297</t>
+          <t>54436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>115100</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100919</t>
+          <t>92459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129907</t>
+          <t>117933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62456</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52651</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72593</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54422</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45388</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63182</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>53,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54879</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78341</t>
+          <t>62790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>121786</t>
+          <t>116737</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106979</t>
+          <t>103625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135967</t>
+          <t>129099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>58,27%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41133</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33009</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49006</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>45754</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37561</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54367</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>46977</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39242</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>55538</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>41,13%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>58,21%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>42667</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34246</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>52144</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>45,53%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>55,65%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>127</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>88422</t>
+          <t>88110</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76345</t>
+          <t>75772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>99618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48747</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40874</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56871</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>47638</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39025</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55831</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>51,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>48433</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>39872</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>56168</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>50,76%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>41,79%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>51041</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>41564</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>59462</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>54,47%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>98679</t>
+          <t>97180</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86923</t>
+          <t>85672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110756</t>
+          <t>109518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26413</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20433</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33505</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19879</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13814</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25930</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48618</t>
+          <t>46585</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38628</t>
+          <t>36913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58132</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29431</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22339</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35411</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30210</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24159</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36275</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>60,31%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>37734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>52419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73794</t>
+          <t>70941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>83828</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70206</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96807</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>69530</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>48115</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85717</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88978</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>57962</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>79724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>152394</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>136014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179643</t>
+          <t>170237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>113485</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100506</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127107</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>146007</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>129820</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167422</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123680</t>
+          <t>108073</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108882</t>
+          <t>96916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136648</t>
+          <t>118678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>269687</t>
+          <t>221559</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248553</t>
+          <t>203716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306332</t>
+          <t>237939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73067</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>60634</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>88946</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>54574</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45419</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>63981</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>47,25%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>53691</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67101</t>
+          <t>45470</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99031</t>
+          <t>62617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>134749</t>
+          <t>126758</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119279</t>
+          <t>110885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156595</t>
+          <t>144841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72519</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>56640</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>84952</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>60935</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>51528</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>70090</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>79285</t>
+          <t>61775</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60430</t>
+          <t>52849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92360</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>140221</t>
+          <t>134294</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118375</t>
+          <t>116211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155691</t>
+          <t>150167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>30947</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>24031</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>38542</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>46,99%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>35368</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>28129</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>42257</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>51,34%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>61,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>35258</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>66206</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56849</t>
+          <t>55662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79149</t>
+          <t>76644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34916</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>27321</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>41832</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>53,01%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>33527</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>26638</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40766</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>59,17%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37302</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29714</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44575</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>70828</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58776</t>
+          <t>59576</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81076</t>
+          <t>80558</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>314141</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>290413</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>340373</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>46,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>42,98%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>50,37%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>272392</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>237436</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>300474</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>42,22%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>340102</t>
+          <t>270733</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310127</t>
+          <t>250770</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>369298</t>
+          <t>292167</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>612494</t>
+          <t>584874</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>568292</t>
+          <t>550092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>651908</t>
+          <t>619401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>361554</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>335322</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>385282</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>53,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>49,63%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>57,02%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>372739</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>344657</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>407695</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>57,78%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53,42%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>63,2%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>392266</t>
+          <t>339499</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363070</t>
+          <t>318065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>422241</t>
+          <t>359462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>765005</t>
+          <t>701053</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>725591</t>
+          <t>666526</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>809207</t>
+          <t>735835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
